--- a/appendix/ПЗ4_Приложение_расчёты_WBS_PERT_CPM_TableMind.xlsx
+++ b/appendix/ПЗ4_Приложение_расчёты_WBS_PERT_CPM_TableMind.xlsx
@@ -199,7 +199,7 @@
     <t xml:space="preserve">12.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Надстройка Excel: проверка при правке, ghost-подсказки, Cmd-K</t>
+    <t xml:space="preserve">Надстройка Excel: проверка при правке и панель находок</t>
   </si>
   <si>
     <t xml:space="preserve">Надстройка для Excel</t>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="B17" s="32" t="str">
         <f aca="false">'Расчёт CPM'!B16</f>
-        <v>Надстройка Excel: проверка при правке, ghost-подсказки, Cmd-K</v>
+        <v>Надстройка Excel: проверка при правке и панель находок</v>
       </c>
       <c r="C17" s="31" t="str">
         <f aca="false">'Расчёт CPM'!C16</f>

--- a/appendix/ПЗ4_Приложение_расчёты_WBS_PERT_CPM_TableMind.xlsx
+++ b/appendix/ПЗ4_Приложение_расчёты_WBS_PERT_CPM_TableMind.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">TableMind: Разработка AI-сервиса проверки Excel-моделей TableMind</t>
+    <t xml:space="preserve">Разработка AI-сервиса проверки Excel-моделей TableMind</t>
   </si>
   <si>
     <t xml:space="preserve">—</t>
@@ -184,7 +184,7 @@
     <t xml:space="preserve">AI-слой и монетизация</t>
   </si>
   <si>
-    <t xml:space="preserve">AI-объяснения и исправления с повторной проверкой</t>
+    <t xml:space="preserve">AI-объяснения и исправления с повторной проверкой; экспорт xlsx и PDF-отчёта</t>
   </si>
   <si>
     <t xml:space="preserve">11.0</t>

--- a/appendix/ПЗ4_Приложение_расчёты_WBS_PERT_CPM_TableMind.xlsx
+++ b/appendix/ПЗ4_Приложение_расчёты_WBS_PERT_CPM_TableMind.xlsx
@@ -4490,6 +4490,17 @@
         <v>46660</v>
       </c>
     </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>Открытая бета веб-аудита с оплатой (после 10.0 и 11.0)</t>
+        </is>
+      </c>
+      <c r="D27" s="36" t="n">
+        <f aca="false">EDATE('Расчёт CPM'!$G$22,8)</f>
+        <v>46539</v>
+      </c>
+    </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="22" t="s">
         <v>174</v>
